--- a/1105/test.xlsx
+++ b/1105/test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lienrueiyu/Desktop/LAB/03collegeproject/01Matlab/1105/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82407A3F-0228-C540-870C-8E1C627B03FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F12391-8CB1-094F-A760-D06212FFCBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19800" xr2:uid="{9222699D-FE95-5345-ACB2-964E3AB48AD8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="14">
   <si>
     <t>Spec Name</t>
   </si>
@@ -78,6 +78,10 @@
   </si>
   <si>
     <t>Spec_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -462,319 +466,340 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F6FA1B8-4B21-B944-995C-0A8304D3ACB7}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <f t="shared" ref="B2" si="0">(D2*E2*F2)^(1/3)</f>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2" si="0">(E2*F2*G2)^(1/3)</f>
         <v>1.2599210498948732</v>
       </c>
-      <c r="C2">
-        <f>AVERAGE(D2:F2)</f>
+      <c r="D2">
+        <f>AVERAGE(E2:G2)</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B12" si="1">(D3*E3*F3)^(1/3)</f>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C7" si="1">(E3*F3*G3)^(1/3)</f>
         <v>1.2599210498948732</v>
       </c>
-      <c r="C3">
-        <f>AVERAGE(D3:F3)</f>
+      <c r="D3">
+        <f>AVERAGE(E3:G3)</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>45</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>135</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <f t="shared" si="1"/>
         <v>1.2599210498948732</v>
       </c>
-      <c r="C4">
-        <f>AVERAGE(D4:F4)</f>
+      <c r="D4">
+        <f>AVERAGE(E4:G4)</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>315</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>45</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <f t="shared" si="1"/>
         <v>1.2599210498948732</v>
       </c>
-      <c r="C5">
-        <f t="shared" ref="C5" si="2">AVERAGE(D5:F5)</f>
+      <c r="D5">
+        <f t="shared" ref="D5" si="2">AVERAGE(E5:G5)</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>315</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>45</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
         <f t="shared" si="1"/>
         <v>0.98648482973218798</v>
       </c>
-      <c r="C6">
-        <f t="shared" ref="C6" si="3">AVERAGE(D6:F6)</f>
-        <v>1</v>
-      </c>
       <c r="D6">
+        <f t="shared" ref="D6" si="3">AVERAGE(E6:G6)</f>
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>1.2</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
       <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>0.8</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
         <f t="shared" si="1"/>
         <v>0.98648482973218798</v>
       </c>
-      <c r="C7">
-        <f t="shared" ref="C7" si="4">AVERAGE(D7:F7)</f>
-        <v>1</v>
-      </c>
       <c r="D7">
+        <f t="shared" ref="D7" si="4">AVERAGE(E7:G7)</f>
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>1.2</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
       <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>0.8</v>
       </c>
-      <c r="G7">
-        <v>90</v>
-      </c>
       <c r="H7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>180</v>
       </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9">
+    <row r="9" spans="1:13">
+      <c r="B9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10">
+    <row r="10" spans="1:13">
+      <c r="B10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="A11">
+    <row r="11" spans="1:13">
+      <c r="B11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="A12">
+    <row r="12" spans="1:13">
+      <c r="B12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
-      <c r="A13">
+    <row r="13" spans="1:13">
+      <c r="B13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14">
+    <row r="14" spans="1:13">
+      <c r="B14">
         <v>13</v>
       </c>
     </row>
